--- a/data/trans_bre/Q45B_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/Q45B_R-Edad-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,99; 13,19</t>
+          <t>7,36; 13,63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,15; 9,92</t>
+          <t>3,22; 9,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,0; 7,04</t>
+          <t>2,24; 7,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>200,11; 1091,41</t>
+          <t>194,48; 1092,23</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>58,54; 399,59</t>
+          <t>65,96; 404,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64,14; 1286,79</t>
+          <t>88,11; 1837,76</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,44; 18,17</t>
+          <t>11,62; 18,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,27; 18,2</t>
+          <t>11,2; 18,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,47; 8,75</t>
+          <t>3,45; 9,02</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>229,61; 662,98</t>
+          <t>222,84; 674,01</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>217,43; 771,88</t>
+          <t>233,31; 717,22</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>89,14; 504,68</t>
+          <t>98,12; 559,36</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,63; 6,93</t>
+          <t>2,74; 7,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,51; 7,33</t>
+          <t>2,62; 7,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,7; 4,9</t>
+          <t>1,69; 4,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>78,56; 521,7</t>
+          <t>80,25; 524,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>54,96; 363,42</t>
+          <t>64,17; 398,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>136,96; 2786,17</t>
+          <t>132,86; 2499,48</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,6; 5,89</t>
+          <t>1,55; 6,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 4,95</t>
+          <t>0,13; 4,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,91; 4,13</t>
+          <t>1,04; 4,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>54,23; 1313,97</t>
+          <t>45,51; 1425,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-8,46; 252,4</t>
+          <t>-6,35; 242,69</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,74; 1478,72</t>
+          <t>63,58; 2076,35</t>
         </is>
       </c>
     </row>
@@ -954,27 +954,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 2,49</t>
+          <t>-1,26; 2,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 2,64</t>
+          <t>-0,77; 2,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,7; 3,24</t>
+          <t>0,69; 3,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-64,13; 346,15</t>
+          <t>-57,46; 465,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-51,27; 796,29</t>
+          <t>-61,56; 552,45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1034,27 +1034,27 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 2,67</t>
+          <t>-0,39; 2,7</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 3,98</t>
+          <t>-0,16; 4,24</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,64; -0,01</t>
+          <t>-2,38; 0,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
           <t>-100,0; —</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>-81,29; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1114,12 +1114,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,13</t>
+          <t>0,0; 2,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 3,55</t>
+          <t>-0,64; 3,25</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-46,1; —</t>
+          <t>-66,97; —</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1194,32 +1194,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,8; 6,87</t>
+          <t>4,74; 6,87</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,79; 6,05</t>
+          <t>3,89; 5,93</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,89; 3,26</t>
+          <t>1,91; 3,28</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>196,86; 418,43</t>
+          <t>195,49; 412,09</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>127,3; 288,7</t>
+          <t>129,46; 283,93</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>150,8; 451,15</t>
+          <t>147,21; 454,57</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/Q45B_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/Q45B_R-Edad-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,36; 13,63</t>
+          <t>7,14; 13,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,22; 9,88</t>
+          <t>3,35; 10,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,24; 7,2</t>
+          <t>2,17; 7,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>194,48; 1092,23</t>
+          <t>201,77; 1036,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>65,96; 404,83</t>
+          <t>62,84; 427,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,11; 1837,76</t>
+          <t>62,8; 1226,11</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,62; 18,42</t>
+          <t>11,43; 18,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,2; 18,11</t>
+          <t>11,17; 18,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,45; 9,02</t>
+          <t>3,27; 8,63</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>222,84; 674,01</t>
+          <t>224,6; 681,83</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>233,31; 717,22</t>
+          <t>236,91; 767,99</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>98,12; 559,36</t>
+          <t>95,73; 568,52</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,74; 7,21</t>
+          <t>2,62; 7,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,62; 7,44</t>
+          <t>2,09; 7,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,69; 4,8</t>
+          <t>1,72; 5,06</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>80,25; 524,13</t>
+          <t>80,56; 505,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>64,17; 398,32</t>
+          <t>47,77; 344,55</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>132,86; 2499,48</t>
+          <t>124,73; 2521,63</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,55; 6,0</t>
+          <t>1,61; 5,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,13; 4,92</t>
+          <t>-0,39; 4,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,04; 4,16</t>
+          <t>1,03; 4,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>45,51; 1425,0</t>
+          <t>47,36; 1037,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-6,35; 242,69</t>
+          <t>-12,44; 256,75</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,58; 2076,35</t>
+          <t>55,36; 1981,15</t>
         </is>
       </c>
     </row>
@@ -954,27 +954,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 2,87</t>
+          <t>-1,32; 2,56</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 2,39</t>
+          <t>-0,55; 2,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,69; 3,24</t>
+          <t>0,7; 3,45</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-57,46; 465,18</t>
+          <t>-62,18; 368,1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-61,56; 552,45</t>
+          <t>-42,65; 903,52</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1034,27 +1034,27 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 2,7</t>
+          <t>-0,7; 2,7</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 4,24</t>
+          <t>-0,31; 4,04</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 0,0</t>
+          <t>-2,38; 0,25</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-75,32; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-65,98; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1114,12 +1114,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,88</t>
+          <t>0,0; 2,18</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 3,25</t>
+          <t>-0,43; 3,32</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-66,97; —</t>
+          <t>-55,9; —</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1194,32 +1194,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,74; 6,87</t>
+          <t>4,85; 6,9</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,89; 5,93</t>
+          <t>3,9; 5,99</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,91; 3,28</t>
+          <t>1,95; 3,27</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>195,49; 412,09</t>
+          <t>198,07; 411,77</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>129,46; 283,93</t>
+          <t>132,9; 280,4</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>147,21; 454,57</t>
+          <t>166,69; 459,51</t>
         </is>
       </c>
     </row>
